--- a/data/sars/alaska/tables/Alaska_2005_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2005_Appendix2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D302D286-77D9-C14D-ABFA-70DADCA71040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDABAC0-C350-834A-9B00-337AF82CAED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17220" yWindow="760" windowWidth="16980" windowHeight="21380" xr2:uid="{1C5FA982-357B-8545-B142-E0C550AC74A6}"/>
+    <workbookView xWindow="5780" yWindow="760" windowWidth="28420" windowHeight="20700" xr2:uid="{1C5FA982-357B-8545-B142-E0C550AC74A6}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2005_Appendix2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="72">
   <si>
     <t>Alaska</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Spotted seal</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -384,7 +390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,6 +568,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -725,7 +737,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -737,6 +749,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1114,17 +1138,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F1A2A5-4BDE-D94D-BD6D-305051131DAC}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.33203125" style="1" customWidth="1"/>
-    <col min="3" max="14" width="10.83203125" style="1"/>
-    <col min="15" max="15" width="10.83203125" style="2"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="10.83203125" style="2"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1167,362 +1191,400 @@
       <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>0.02</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="5">
         <v>0.5</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="K2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
         <v>0.06</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="5">
         <v>0.5</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="K3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
         <v>1.6</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="7">
         <v>6788</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="O3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <v>39258</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="5">
         <v>0.22900000000000001</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>2</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
         <v>0.22900000000000001</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="7">
         <v>32453</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="5">
         <v>0.02</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="5">
         <v>0.5</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="5">
         <v>324</v>
       </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
         <v>152</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="O4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>3710</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
         <v>3.09</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <v>3710</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="5">
         <v>0.02</v>
       </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
         <v>74</v>
       </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
         <v>65</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="O5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <v>18142</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="5">
         <v>0.24</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="5">
         <v>3.09</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
         <v>0.24</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="7">
         <v>14898</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="5">
         <v>0.02</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
         <v>298</v>
       </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
         <v>209</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="O6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="7">
         <v>1888</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
         <v>3.09</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>0.2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="7">
         <v>1619</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="5">
         <v>0.02</v>
       </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
         <v>32</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="5">
         <v>0.5</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="5">
         <v>19</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="O7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>357</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="5">
         <v>0.107</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="5">
         <v>0.107</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="5">
         <v>326</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="5">
         <v>0.02</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="5">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="5">
         <v>2</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="7">
         <v>10545</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>0.128</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>0.128</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="7">
         <v>9472</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="5">
         <v>0.02</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="5">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="5">
         <v>95</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="5">
         <v>0.2</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="5">
         <v>41</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="O9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="B10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
         <v>0.02</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="5">
         <v>0.5</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="K10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -1557,83 +1619,91 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="5">
         <v>5703</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="5">
         <v>0.2</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="5">
         <v>5703</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="5">
         <v>0.02</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="5">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="5">
         <v>11.4</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="5">
         <v>0.6</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="O12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="7">
         <v>18813</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="5">
         <v>0.09</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="7">
         <v>17752</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="5">
         <v>2.35E-2</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
         <v>442</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="5">
         <v>7.4</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M13" s="5">
         <v>122</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1676,11 +1746,11 @@
       <c r="N14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="P14" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1723,11 +1793,11 @@
       <c r="N15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1770,11 +1840,11 @@
       <c r="N16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="P16" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1817,9 +1887,9 @@
       <c r="N17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="4"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1863,7 +1933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1907,303 +1977,330 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="5">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="5">
         <v>367</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="5">
         <v>0.1</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="5">
         <v>1.3</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="5">
         <v>0.69</v>
       </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="7">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="7">
         <v>3698</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="5">
         <v>0.1</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="5">
         <v>12.9</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="5">
         <v>4.2</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="5">
         <v>961</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="5">
         <v>0.12</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="5">
         <v>0.12</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="5">
         <v>868</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="5">
         <v>0.1</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="5">
         <v>3</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="5">
         <v>2.7</v>
       </c>
-      <c r="O22" s="4"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="O22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="7">
         <v>1123</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="D23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="7">
         <v>1123</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="5">
         <v>0.02</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="5">
         <v>0.5</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="5">
         <v>11.2</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="5">
         <v>216</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="D24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
         <v>216</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="5">
         <v>0.02</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="5">
         <v>0.5</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="5">
         <v>2.16</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1" t="s">
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="O24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="5">
         <v>8</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="D25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5">
         <v>8</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="5">
         <v>0.02</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="5">
         <v>0.5</v>
       </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="O25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="5">
         <v>314</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="D26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5">
         <v>314</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="5">
         <v>0.02</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="5">
         <v>0.5</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="5">
         <v>3.1</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="M26" s="5">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="5">
         <v>314</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="D27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5">
         <v>314</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="5">
         <v>0.02</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="5">
         <v>0.5</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="5">
         <v>3.1</v>
       </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1" t="s">
+      <c r="L27" s="5">
+        <v>0</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2235,80 +2332,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="C29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5">
         <v>0.02</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="5">
         <v>0.1</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="K29" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="O29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="7">
         <v>688028</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="5">
         <v>4.4749999999999996</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
         <v>0.2</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="7">
         <v>676540</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="5">
         <v>0.5</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="7">
         <v>14546</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="5">
         <v>15</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="5">
         <v>869</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
@@ -2340,229 +2445,257 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="B32" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5">
         <v>0.06</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="5">
         <v>0.5</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1">
+      <c r="K32" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" s="5">
         <v>0.8</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32" s="5">
         <v>193</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="N32" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="O32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="B33" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5">
         <v>0.06</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="5">
         <v>0.5</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="K33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="5">
         <v>0.7</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="7">
         <v>9567</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N33" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="O33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="C34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5">
         <v>0.02</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="5">
         <v>0.1</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1">
+      <c r="K34" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5">
         <v>0.5</v>
       </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="M34" s="5">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="O34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="B35" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5">
         <v>0.06</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="5">
         <v>0.5</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="K35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5">
         <v>2</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="7">
         <v>5265</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+      <c r="O35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
+      <c r="B36" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5">
         <v>0.02</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="5">
         <v>0.5</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="s">
+      <c r="K36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="O36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="7">
         <v>44996</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="7">
         <v>43728</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="5">
         <v>0.06</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="5">
         <v>0.75</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="7">
         <v>1967</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="5">
         <v>5.3</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="5">
         <v>4</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N37" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="O37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="7">
         <v>38513</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="7">
         <v>38513</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="5">
         <v>0.06</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="5">
         <v>0.1</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="5">
         <v>231</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="5">
         <v>30.9</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="5">
         <v>187</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="N38" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="O38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P38" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
